--- a/output/pdf_financials_xlsx/JUGR.xlsx
+++ b/output/pdf_financials_xlsx/JUGR.xlsx
@@ -1234,10 +1234,10 @@
         <v>-0.5372130000000001</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.133644</v>
+        <v>-0.133644</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.133644</v>
+        <v>-0.133644</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>-0.107086</v>
@@ -1277,7 +1277,7 @@
         <v>0.015067</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0.672416</v>
+        <v>-0</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>-0</v>
@@ -1506,7 +1506,7 @@
         <v>-0.549513</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.336208</v>
+        <v>-0.336208</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>-4.177864</v>
@@ -1518,10 +1518,10 @@
         <v>-0.5372130000000001</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.133644</v>
+        <v>-0.133644</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.133644</v>
+        <v>-0.133644</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>-0.107086</v>
@@ -1671,7 +1671,7 @@
         <v>-0.549513</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.336208</v>
+        <v>-0.336208</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>-4.177864</v>
@@ -1683,10 +1683,10 @@
         <v>-0.5372130000000001</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.133644</v>
+        <v>-0.133644</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.133644</v>
+        <v>-0.133644</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>-0.107086</v>
@@ -1836,7 +1836,7 @@
         <v>18.3171</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>-11.206933</v>
+        <v>11.206933</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>26.11165</v>
@@ -1848,7 +1848,7 @@
         <v>3.357581</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>-1.67055</v>
+        <v>1.67055</v>
       </c>
       <c r="H26" s="1" t="inlineStr">
         <is>
@@ -1909,10 +1909,10 @@
         <v>-0.5372130000000001</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.133644</v>
+        <v>-0.133644</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.133644</v>
+        <v>-0.133644</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-0.107086</v>
@@ -2019,10 +2019,10 @@
         <v>-0.537048</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.133776</v>
+        <v>-0.133512</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.13375</v>
+        <v>-0.133538</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-0.107001</v>
@@ -2149,7 +2149,7 @@
         <v>-2.66870948315562</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>-200</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>-0</v>
@@ -2161,10 +2161,10 @@
         <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>-0</v>
@@ -5721,19 +5721,19 @@
         <v>0.035838</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>2.016633</v>
+        <v>1.946058</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.879399</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.828778</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.386293</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.386293</v>
       </c>
       <c r="I92" s="3" t="n">
         <v>0</v>
@@ -6313,25 +6313,25 @@
         <v>0</v>
       </c>
       <c r="K103" s="3" t="n">
-        <v>0</v>
+        <v>-0.170896</v>
       </c>
       <c r="L103" s="3" t="n">
-        <v>0</v>
+        <v>0.071783</v>
       </c>
       <c r="M103" s="3" t="n">
-        <v>0</v>
+        <v>-0.09267300000000001</v>
       </c>
       <c r="N103" s="3" t="n">
-        <v>0</v>
+        <v>-0.246586</v>
       </c>
       <c r="O103" s="3" t="n">
-        <v>0</v>
+        <v>-0.124098</v>
       </c>
       <c r="P103" s="3" t="n">
-        <v>0</v>
+        <v>-0.36908</v>
       </c>
       <c r="Q103" s="3" t="n">
-        <v>0</v>
+        <v>-0.226521</v>
       </c>
     </row>
     <row r="104">
@@ -6478,25 +6478,25 @@
         <v>-0.013291</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>0.120464</v>
+        <v>-0.050432</v>
       </c>
       <c r="L106" s="3" t="n">
-        <v>0.158979</v>
+        <v>0.230762</v>
       </c>
       <c r="M106" s="3" t="n">
-        <v>0.281035</v>
+        <v>0.188362</v>
       </c>
       <c r="N106" s="3" t="n">
-        <v>0.093641</v>
+        <v>-0.152945</v>
       </c>
       <c r="O106" s="3" t="n">
-        <v>0.275854</v>
+        <v>0.151756</v>
       </c>
       <c r="P106" s="3" t="n">
-        <v>1.35634</v>
+        <v>0.98726</v>
       </c>
       <c r="Q106" s="3" t="n">
-        <v>1.006651</v>
+        <v>0.78013</v>
       </c>
     </row>
     <row r="107">
@@ -7120,10 +7120,10 @@
         <v>0</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>1.028125</v>
+        <v>1.023894</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0.205196</v>
+        <v>-0.004043</v>
       </c>
       <c r="G118" s="3" t="n">
         <v>0</v>
@@ -8510,7 +8510,11 @@
           <t>Prepaid and deposits (Notes 6)</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>-</t>
@@ -10242,7 +10246,11 @@
           <t>Prepaid and deposits (Notes 6 and 10)</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
@@ -10910,7 +10918,11 @@
           <t>Prepaid and deposits (Note 6)</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
@@ -12028,7 +12040,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
@@ -13366,7 +13382,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>-</t>
@@ -14218,7 +14238,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>-</t>
@@ -17818,7 +17842,11 @@
           <t>Prepaid and deposits</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
           <t>-</t>
@@ -23262,7 +23290,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr"/>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr">
         <is>
           <t>-</t>
@@ -24324,7 +24356,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr"/>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E173" t="inlineStr">
         <is>
           <t>-</t>
@@ -35479,7 +35515,7 @@
         </is>
       </c>
       <c r="J291" s="5" t="n">
-        <v>0.133644</v>
+        <v>-0.133644</v>
       </c>
       <c r="K291" t="inlineStr">
         <is>
@@ -37493,10 +37529,10 @@
         </is>
       </c>
       <c r="J312" s="5" t="n">
-        <v>0.262316</v>
+        <v>-0.262316</v>
       </c>
       <c r="K312" s="5" t="n">
-        <v>0.133644</v>
+        <v>-0.133644</v>
       </c>
       <c r="L312" t="inlineStr">
         <is>
@@ -42529,10 +42565,10 @@
         </is>
       </c>
       <c r="F365" s="5" t="n">
-        <v>0.336208</v>
+        <v>-0.336208</v>
       </c>
       <c r="G365" s="5" t="n">
-        <v>4.212601</v>
+        <v>-4.212601</v>
       </c>
       <c r="H365" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/JUGR.xlsx
+++ b/output/pdf_financials_xlsx/JUGR.xlsx
@@ -1026,25 +1026,25 @@
         <v>0</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.012425</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.028733</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.010227</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.027475</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.06730700000000001</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.03856</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.105229</v>
       </c>
     </row>
     <row r="13">
@@ -1921,25 +1921,25 @@
         <v>-0.394471</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.770132</v>
+        <v>-0.7825569999999999</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-6.437092</v>
+        <v>-6.465825</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.84674</v>
+        <v>-0.856967</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.138557</v>
+        <v>-0.166032</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-6.602542</v>
+        <v>-6.669849</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-1.394148</v>
+        <v>-1.432708</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-2.980581</v>
+        <v>-3.08581</v>
       </c>
     </row>
     <row r="28">
@@ -2031,25 +2031,25 @@
         <v>-0.394403</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.768946</v>
+        <v>-0.781371</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-6.434584</v>
+        <v>-6.463317</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.839189</v>
+        <v>-0.8494159999999999</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.123984</v>
+        <v>-0.151459</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-6.58986</v>
+        <v>-6.657167</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-1.381836</v>
+        <v>-1.420396</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-2.970098</v>
+        <v>-3.075327</v>
       </c>
     </row>
     <row r="30">
@@ -2295,28 +2295,28 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.099703</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.013234</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>7.8e-05</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.001531</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.003882</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.000797</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.004251</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.1515</v>
       </c>
       <c r="J34" s="1" t="inlineStr">
         <is>
@@ -2409,28 +2409,28 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.099703</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.013234</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>7.8e-05</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.001531</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.003882</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.000797</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.004251</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.1515</v>
       </c>
       <c r="J36" s="1" t="inlineStr">
         <is>
@@ -3093,28 +3093,28 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.099703</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.013234</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.001297</v>
+        <v>0.001219</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.001531</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.004135</v>
+        <v>0.000253</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.000797</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.004251</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.1515</v>
+        <v>0</v>
       </c>
       <c r="J48" s="1" t="inlineStr">
         <is>
@@ -11210,7 +11210,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -14702,7 +14702,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E70" s="5" t="n">
@@ -30100,7 +30100,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -30916,7 +30916,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">

--- a/output/pdf_financials_xlsx/JUGR.xlsx
+++ b/output/pdf_financials_xlsx/JUGR.xlsx
@@ -745,7 +745,7 @@
         <v>0.0435</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0</v>
+        <v>0.029</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>0.04203</v>
@@ -855,7 +855,7 @@
         <v>0.027888</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>0.012688</v>
+        <v>0.024688</v>
       </c>
       <c r="J9" s="3" t="n">
         <v>0.160958</v>
@@ -910,7 +910,7 @@
         <v>0.156419</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.012688</v>
+        <v>0.053688</v>
       </c>
       <c r="J10" s="3" t="n">
         <v>0.202988</v>
@@ -965,7 +965,7 @@
         <v>-0.156419</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-0.012688</v>
+        <v>-0.053688</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>-0.394471</v>
@@ -33264,7 +33264,11 @@
           <t>Consulting – Note 4</t>
         </is>
       </c>
-      <c r="D268" t="inlineStr"/>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E268" t="inlineStr">
         <is>
           <t>-</t>
@@ -33550,7 +33554,11 @@
           <t>Management fees – Note 4</t>
         </is>
       </c>
-      <c r="D271" t="inlineStr"/>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E271" t="inlineStr">
         <is>
           <t>-</t>
@@ -33738,7 +33746,11 @@
           <t>Professional fees – Note 4</t>
         </is>
       </c>
-      <c r="D273" t="inlineStr"/>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E273" t="inlineStr">
         <is>
           <t>-</t>
